--- a/Dynamics BC Excel Reports/ReportLayouts/Excel/FixedAsset/FixedAssetAnalysisExcel.xlsx
+++ b/Dynamics BC Excel Reports/ReportLayouts/Excel/FixedAsset/FixedAssetAnalysisExcel.xlsx
@@ -1,88 +1,88 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr hidePivotFieldList="1"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <x:workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.williams\Source\Gold\Yellowstone.Apps\Apps\W1\ExcelReports\app\ReportLayouts\Excel\FixedAsset\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F90A69-F253-41C3-971A-B4FEEDDC0764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="$FixedAssetAnalysisPrint$" sheetId="12" r:id="rId1"/>
-    <sheet name="$FixedAssetAnalysis$" sheetId="7" r:id="rId2"/>
-    <sheet name="$BookValue$" sheetId="10" r:id="rId3"/>
-    <sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId4"/>
-    <sheet name="$AboutTheReportLabel$" sheetId="13" r:id="rId5"/>
-    <sheet name="FixedAssetData" sheetId="5" state="hidden" r:id="rId6"/>
-    <sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId7"/>
-    <sheet name="Metadata" sheetId="9" state="hidden" r:id="rId8"/>
-    <sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId9"/>
-  </sheets>
-  <definedNames>
-    <definedName name="AcquisitionCost">Metadata!$A$10</definedName>
-    <definedName name="Caption.Amount2LCY" comment="Use this function to get the Amount2LCY from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("Amount2LCY",#REF!,#REF!,"none",)</definedName>
-    <definedName name="Caption.AmountLCY" comment="Use this function to get the AmountLCY from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("AmountLCY",#REF!,#REF!,"none",)</definedName>
-    <definedName name="Caption.CustomerName" comment="Use this function to get the CustomerName from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("CustomerName",#REF!,#REF!,"none",)</definedName>
-    <definedName name="Caption.CustomerNo" comment="Use this function to get the CustomerNo from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("CustomerNo",#REF!,#REF!,"none",)</definedName>
-    <definedName name="Caption.DataRetrieved" comment="Use this function to get the DataRetrieved from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("DataRetrieved",#REF!,#REF!,"none",)</definedName>
-    <definedName name="Caption.DateFilterLabel" comment="Use this function to get the DateFilterLabel from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("DateFilterLabel",#REF!,#REF!,"none",)</definedName>
-    <definedName name="Caption.RankAccordingTo" comment="Use this function to get the RankAccordingTo from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("RankAccordingTo",#REF!,#REF!,"none",)</definedName>
-    <definedName name="Caption.TopCustomerListLabel" comment="Use this function to get the TopCustomerListLabel from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("TopCustomerListLabel",#REF!,#REF!,"none",)</definedName>
-    <definedName name="CompanyName">Metadata!$A$1</definedName>
-    <definedName name="DataRetrieved">Metadata!$A$6</definedName>
-    <definedName name="Depreciation">Metadata!$A$9</definedName>
-    <definedName name="DepreciationBook">Metadata!$A$7</definedName>
-    <definedName name="DepreciationBookCode">Metadata!$A$3</definedName>
-    <definedName name="EndingDate">Metadata!$A$5</definedName>
-    <definedName name="Period">Metadata!$A$8</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionID" comment="Use this function to get the Extension ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension ID",#REF!,#REF!,"none",)</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyDisplayName" comment="Use this function to get the Company display name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company display name",#REF!,#REF!,"none",)</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="RetrievedAt">Metadata!$A$2</definedName>
-    <definedName name="Slicer_BudgetedAsset">#N/A</definedName>
-    <definedName name="Slicer_BudgetedAsset1">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetClassCode">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetClassCode1">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetLocationCode">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetLocationCode1">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetSubclassCode">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetSubclassCode1">#N/A</definedName>
-    <definedName name="Slicer_GlobalDimension1Code">#N/A</definedName>
-    <definedName name="Slicer_GlobalDimension1Code1">#N/A</definedName>
-    <definedName name="Slicer_GlobalDimension2Code">#N/A</definedName>
-    <definedName name="Slicer_GlobalDimension2Code1">#N/A</definedName>
-    <definedName name="StartingDate">Metadata!$A$4</definedName>
-  </definedNames>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId10"/>
-    <pivotCache cacheId="1" r:id="rId11"/>
-    <pivotCache cacheId="4" r:id="rId12"/>
-  </pivotCaches>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+  <x:bookViews>
+    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="$FixedAssetAnalysisPrint$" sheetId="12" r:id="rId1"/>
+    <x:sheet name="$FixedAssetAnalysis$" sheetId="7" r:id="rId2"/>
+    <x:sheet name="$BookValue$" sheetId="10" r:id="rId3"/>
+    <x:sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId4"/>
+    <x:sheet name="$AboutTheReportLabel$" sheetId="13" r:id="rId5"/>
+    <x:sheet name="FixedAssetData" sheetId="5" state="hidden" r:id="rId6"/>
+    <x:sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId7"/>
+    <x:sheet name="Metadata" sheetId="9" state="hidden" r:id="rId8"/>
+    <x:sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId9"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="AcquisitionCost">Metadata!$A$10</x:definedName>
+    <x:definedName name="Caption.Amount2LCY" comment="Use this function to get the Amount2LCY from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("Amount2LCY",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="Caption.AmountLCY" comment="Use this function to get the AmountLCY from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("AmountLCY",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="Caption.CustomerName" comment="Use this function to get the CustomerName from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("CustomerName",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="Caption.CustomerNo" comment="Use this function to get the CustomerNo from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("CustomerNo",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="Caption.DataRetrieved" comment="Use this function to get the DataRetrieved from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("DataRetrieved",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="Caption.DateFilterLabel" comment="Use this function to get the DateFilterLabel from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("DateFilterLabel",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="Caption.RankAccordingTo" comment="Use this function to get the RankAccordingTo from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("RankAccordingTo",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="Caption.TopCustomerListLabel" comment="Use this function to get the TopCustomerListLabel from the CaptionData table in the CaptionData worksheet">_xlfn.XLOOKUP("TopCustomerListLabel",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="CompanyName">Metadata!$A$1</x:definedName>
+    <x:definedName name="DataRetrieved">Metadata!$A$6</x:definedName>
+    <x:definedName name="Depreciation">Metadata!$A$9</x:definedName>
+    <x:definedName name="DepreciationBook">Metadata!$A$7</x:definedName>
+    <x:definedName name="DepreciationBookCode">Metadata!$A$3</x:definedName>
+    <x:definedName name="EndingDate">Metadata!$A$5</x:definedName>
+    <x:definedName name="Period">Metadata!$A$8</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionID" comment="Use this function to get the Extension ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension ID",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyDisplayName" comment="Use this function to get the Company display name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company display name",#REF!,#REF!,"none",)</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="RetrievedAt">Metadata!$A$2</x:definedName>
+    <x:definedName name="Slicer_BudgetedAsset">#N/A</x:definedName>
+    <x:definedName name="Slicer_BudgetedAsset1">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetClassCode">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetClassCode1">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetLocationCode">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetLocationCode1">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetSubclassCode">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetSubclassCode1">#N/A</x:definedName>
+    <x:definedName name="Slicer_GlobalDimension1Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_GlobalDimension1Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_GlobalDimension2Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_GlobalDimension2Code1">#N/A</x:definedName>
+    <x:definedName name="StartingDate">Metadata!$A$4</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029" forceFullCalc="1"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="0" r:id="rId10"/>
+    <x:pivotCache cacheId="1" r:id="rId11"/>
+    <x:pivotCache cacheId="4" r:id="rId12"/>
+  </x:pivotCaches>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId13"/>
         <x14:slicerCache r:id="rId14"/>
@@ -97,11 +97,11 @@
         <x14:slicerCache r:id="rId23"/>
         <x14:slicerCache r:id="rId24"/>
       </x14:slicerCaches>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+    </x:ext>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    </x:ext>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -111,9 +111,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6030,29 +6030,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FF753DCC-0195-4965-9428-64C93A0FBD7A}" name="FixedAssetData" displayName="FixedAssetData" ref="A1:O2" insertRow="1" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
-  <autoFilter ref="A1:O2" xr:uid="{FF753DCC-0195-4965-9428-64C93A0FBD7A}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{BB724618-0C06-4B17-86F5-AF5A7955BE16}" name="FixedAssetPostingTypeNumber" dataDxfId="106"/>
-    <tableColumn id="2" xr3:uid="{64440C09-B4D6-4B19-BF16-5F4E69114404}" name="FixedAssetPostingTypeName" dataDxfId="105"/>
-    <tableColumn id="3" xr3:uid="{41194416-A3A9-4CDF-93EA-0546B745562B}" name="BeforeStartingDate" dataDxfId="104"/>
-    <tableColumn id="4" xr3:uid="{ACBC4539-DDAC-4F86-B1AA-0EF5622D35E3}" name="AtEndingDate" dataDxfId="103"/>
-    <tableColumn id="5" xr3:uid="{531FF9B9-5E37-4B76-8D5C-4DC89DA92944}" name="NetChange" dataDxfId="102"/>
-    <tableColumn id="6" xr3:uid="{2608504A-F084-4D8D-BB26-9C0552CE6821}" name="AssetNumber" dataDxfId="101"/>
-    <tableColumn id="7" xr3:uid="{DF54F312-8F38-4A23-AC17-33B73D568E17}" name="AssetDescription" dataDxfId="100"/>
-    <tableColumn id="8" xr3:uid="{98A1927A-207D-4E0D-B860-A041EBF80F6C}" name="FixedAssetClassCode" dataDxfId="99"/>
-    <tableColumn id="9" xr3:uid="{8B7B4BA3-5CC4-4CC1-9A27-1B2CC1F98EC4}" name="FixedAssetSubclassCode" dataDxfId="98"/>
-    <tableColumn id="10" xr3:uid="{908C60C1-574F-44EF-85B9-01C802CFF2A9}" name="FixedAssetLocationCode" dataDxfId="97"/>
-    <tableColumn id="11" xr3:uid="{3C1F412D-4620-45BE-AF10-A65BE9BC6181}" name="BudgetedAsset" dataDxfId="96">
-      <calculatedColumnFormula>FALSE()</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" xr3:uid="{1FCB446F-6A62-48F6-92BC-13E4390E401F}" name="AcquisitionDateField" dataDxfId="95"/>
-    <tableColumn id="13" xr3:uid="{B9297C33-A40D-437C-B123-B0BDF7D80F44}" name="DisposalDateField" dataDxfId="94"/>
-    <tableColumn id="14" xr3:uid="{6DD0F39A-4567-49E5-9608-CA923A2649A5}" name="GlobalDimension1Code" dataDxfId="93"/>
-    <tableColumn id="15" xr3:uid="{4B02829C-67B9-4248-A832-04D019F740C8}" name="GlobalDimension2Code" dataDxfId="92"/>
-  </tableColumns>
-  <tableStyleInfo name="Business Central Reports Table Style (Template)" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FixedAssetData" displayName="FixedAssetData" ref="A1:O2" insertRow="1" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107" xr:uid="{FF753DCC-0195-4965-9428-64C93A0FBD7A}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:O2" xr:uid="{FF753DCC-0195-4965-9428-64C93A0FBD7A}"/>
+  <x:tableColumns count="15">
+    <x:tableColumn id="1" name="FixedAssetPostingTypeNumber" dataDxfId="106" xr3:uid="{BB724618-0C06-4B17-86F5-AF5A7955BE16}"/>
+    <x:tableColumn id="2" name="FixedAssetPostingTypeName" dataDxfId="105" xr3:uid="{64440C09-B4D6-4B19-BF16-5F4E69114404}"/>
+    <x:tableColumn id="3" name="BeforeStartingDate" dataDxfId="104" xr3:uid="{41194416-A3A9-4CDF-93EA-0546B745562B}"/>
+    <x:tableColumn id="4" name="AtEndingDate" dataDxfId="103" xr3:uid="{ACBC4539-DDAC-4F86-B1AA-0EF5622D35E3}"/>
+    <x:tableColumn id="5" name="NetChange" dataDxfId="102" xr3:uid="{531FF9B9-5E37-4B76-8D5C-4DC89DA92944}"/>
+    <x:tableColumn id="6" name="AssetNumber" dataDxfId="101" xr3:uid="{2608504A-F084-4D8D-BB26-9C0552CE6821}"/>
+    <x:tableColumn id="7" name="AssetDescription" dataDxfId="100" xr3:uid="{DF54F312-8F38-4A23-AC17-33B73D568E17}"/>
+    <x:tableColumn id="8" name="FixedAssetClassCode" dataDxfId="99" xr3:uid="{98A1927A-207D-4E0D-B860-A041EBF80F6C}"/>
+    <x:tableColumn id="9" name="FixedAssetSubclassCode" dataDxfId="98" xr3:uid="{8B7B4BA3-5CC4-4CC1-9A27-1B2CC1F98EC4}"/>
+    <x:tableColumn id="10" name="FixedAssetLocationCode" dataDxfId="97" xr3:uid="{908C60C1-574F-44EF-85B9-01C802CFF2A9}"/>
+    <x:tableColumn id="11" name="BudgetedAsset" dataDxfId="96" xr3:uid="{3C1F412D-4620-45BE-AF10-A65BE9BC6181}">
+      <x:calculatedColumnFormula>FALSE()</x:calculatedColumnFormula>
+    </x:tableColumn>
+    <x:tableColumn id="12" name="AcquisitionDateField" dataDxfId="95" xr3:uid="{1FCB446F-6A62-48F6-92BC-13E4390E401F}"/>
+    <x:tableColumn id="13" name="DisposalDateField" dataDxfId="94" xr3:uid="{B9297C33-A40D-437C-B123-B0BDF7D80F44}"/>
+    <x:tableColumn id="14" name="GlobalDimension1Code" dataDxfId="93" xr3:uid="{6DD0F39A-4567-49E5-9608-CA923A2649A5}"/>
+    <x:tableColumn id="15" name="GlobalDimension2Code" dataDxfId="92" xr3:uid="{4B02829C-67B9-4248-A832-04D019F740C8}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="Business Central Reports Table Style (Template)" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
